--- a/labeled/Add_Eating/July/multi_seed_results/seed_202/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_202/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,1162 +442,746 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6.646825313568115</v>
+        <v>17.39999961853027</v>
       </c>
       <c r="B2" t="n">
-        <v>4.845231533050537</v>
+        <v>12.14140033721924</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6.206896781921387</v>
+        <v>27.32615089416504</v>
       </c>
       <c r="B3" t="n">
-        <v>7.785429954528809</v>
+        <v>17.34981346130371</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73.40000152587891</v>
+        <v>7.783251285552979</v>
       </c>
       <c r="B4" t="n">
-        <v>72.5987548828125</v>
+        <v>10.42811584472656</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>19.84127044677734</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B5" t="n">
-        <v>16.75000190734863</v>
+        <v>24.95080375671387</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7.783251285552979</v>
+        <v>10.7737512588501</v>
       </c>
       <c r="B6" t="n">
-        <v>8.892216682434082</v>
+        <v>13.48953342437744</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14.20176315307617</v>
+        <v>17.46031761169434</v>
       </c>
       <c r="B7" t="n">
-        <v>17.98657608032227</v>
+        <v>9.034798622131348</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5.320197105407715</v>
+        <v>39.5</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09067440032959</v>
+        <v>58.95538330078125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>20.33730125427246</v>
       </c>
       <c r="B9" t="n">
-        <v>23.93707084655762</v>
+        <v>17.05971336364746</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59.52381134033203</v>
+        <v>11.65524005889893</v>
       </c>
       <c r="B10" t="n">
-        <v>54.48645782470703</v>
+        <v>10.95468521118164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="B11" t="n">
-        <v>50.67671585083008</v>
+        <v>27.87615013122559</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>18.75</v>
+        <v>12.5</v>
       </c>
       <c r="B12" t="n">
-        <v>15.99414443969727</v>
+        <v>11.03135585784912</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25.5238094329834</v>
+        <v>26.05288887023926</v>
       </c>
       <c r="B13" t="n">
-        <v>24.2365837097168</v>
+        <v>24.68854141235352</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14.6245059967041</v>
+        <v>42.19047546386719</v>
       </c>
       <c r="B14" t="n">
-        <v>15.16023635864258</v>
+        <v>23.81199073791504</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17.80952453613281</v>
+        <v>24.68168449401855</v>
       </c>
       <c r="B15" t="n">
-        <v>16.16630363464355</v>
+        <v>12.23088645935059</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14.58333301544189</v>
+        <v>35.5</v>
       </c>
       <c r="B16" t="n">
-        <v>14.84653949737549</v>
+        <v>26.1938533782959</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>28</v>
+        <v>10.47992134094238</v>
       </c>
       <c r="B17" t="n">
-        <v>32.44277572631836</v>
+        <v>11.86438274383545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>39.78174591064453</v>
+        <v>6.646825313568115</v>
       </c>
       <c r="B18" t="n">
-        <v>39.37010192871094</v>
+        <v>12.17951774597168</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21.13095283508301</v>
+        <v>6.660137176513672</v>
       </c>
       <c r="B19" t="n">
-        <v>18.23400688171387</v>
+        <v>12.61538410186768</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21.82539749145508</v>
+        <v>14.66666698455811</v>
       </c>
       <c r="B20" t="n">
-        <v>18.03315353393555</v>
+        <v>23.75481224060059</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>38.39373016357422</v>
+        <v>11.14285755157471</v>
       </c>
       <c r="B21" t="n">
-        <v>32.4404182434082</v>
+        <v>12.83361625671387</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>29.79999923706055</v>
+        <v>68.5</v>
       </c>
       <c r="B22" t="n">
-        <v>20.39421081542969</v>
+        <v>65.37741088867188</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>69.90476226806641</v>
+        <v>10.89999961853027</v>
       </c>
       <c r="B23" t="n">
-        <v>63.31453704833984</v>
+        <v>31.43728256225586</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27.81586647033691</v>
+        <v>16.29999923706055</v>
       </c>
       <c r="B24" t="n">
-        <v>27.31503677368164</v>
+        <v>15.84602069854736</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>51.59999847412109</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="B25" t="n">
-        <v>45.4679069519043</v>
+        <v>16.22713851928711</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>36.29999923706055</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="B26" t="n">
-        <v>33.92412185668945</v>
+        <v>24.12758255004883</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9.027777671813965</v>
+        <v>61.40000152587891</v>
       </c>
       <c r="B27" t="n">
-        <v>8.213887214660645</v>
+        <v>58.07489395141602</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8.380952835083008</v>
+        <v>51.59999847412109</v>
       </c>
       <c r="B28" t="n">
-        <v>26.85152435302734</v>
+        <v>14.28430080413818</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3.917727708816528</v>
+        <v>46.20000076293945</v>
       </c>
       <c r="B29" t="n">
-        <v>10.36193656921387</v>
+        <v>32.64749526977539</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8.227228164672852</v>
+        <v>23.21428489685059</v>
       </c>
       <c r="B30" t="n">
-        <v>9.61054801940918</v>
+        <v>18.00613021850586</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>44.46620941162109</v>
+        <v>36.5</v>
       </c>
       <c r="B31" t="n">
-        <v>37.835205078125</v>
+        <v>23.88659858703613</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12.30158710479736</v>
+        <v>26.09127044677734</v>
       </c>
       <c r="B32" t="n">
-        <v>11.34697723388672</v>
+        <v>26.11601257324219</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>97.94319152832031</v>
+        <v>28.7952995300293</v>
       </c>
       <c r="B33" t="n">
-        <v>92.71440124511719</v>
+        <v>33.41268157958984</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33.90000152587891</v>
+        <v>53.90000152587891</v>
       </c>
       <c r="B34" t="n">
-        <v>16.69083976745605</v>
+        <v>43.15687942504883</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>30.15872955322266</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="B35" t="n">
-        <v>23.28441619873047</v>
+        <v>56.58610916137695</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>58</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="B36" t="n">
-        <v>51.84310913085938</v>
+        <v>15.47345352172852</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>74.28571319580078</v>
+        <v>39.09999847412109</v>
       </c>
       <c r="B37" t="n">
-        <v>71.14609527587891</v>
+        <v>50.32462692260742</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B38" t="n">
-        <v>56.73428726196289</v>
+        <v>46.17827606201172</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13.51616096496582</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="B39" t="n">
-        <v>14.61659240722656</v>
+        <v>60.35586929321289</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>78.90000152587891</v>
+        <v>14.6245059967041</v>
       </c>
       <c r="B40" t="n">
-        <v>73.44004058837891</v>
+        <v>17.66512680053711</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>25.39682579040527</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="B41" t="n">
-        <v>18.80481719970703</v>
+        <v>21.29714012145996</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11.43984222412109</v>
+        <v>5.320197105407715</v>
       </c>
       <c r="B42" t="n">
-        <v>12.79928874969482</v>
+        <v>7.669412136077881</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>92.90000152587891</v>
+        <v>36.23898315429688</v>
       </c>
       <c r="B43" t="n">
-        <v>90.31477355957031</v>
+        <v>19.67803192138672</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>44.57143020629883</v>
+        <v>10.34482765197754</v>
       </c>
       <c r="B44" t="n">
-        <v>57.23471069335938</v>
+        <v>10.01017189025879</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>54.29999923706055</v>
+        <v>42.09999847412109</v>
       </c>
       <c r="B45" t="n">
-        <v>51.89686584472656</v>
+        <v>38.00358963012695</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>30.66666603088379</v>
+        <v>91.5</v>
       </c>
       <c r="B46" t="n">
-        <v>23.54351234436035</v>
+        <v>91.36431884765625</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>26.09127044677734</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="B47" t="n">
-        <v>20.57485389709473</v>
+        <v>16.25740623474121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16.96428489685059</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="B48" t="n">
-        <v>15.17675399780273</v>
+        <v>18.67424011230469</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>30.85210609436035</v>
+        <v>6.502462863922119</v>
       </c>
       <c r="B49" t="n">
-        <v>24.74951171875</v>
+        <v>6.844168186187744</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>15.0476188659668</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B50" t="n">
-        <v>22.03486824035645</v>
+        <v>24.36440658569336</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>80</v>
+        <v>17.53183174133301</v>
       </c>
       <c r="B51" t="n">
-        <v>73.59893798828125</v>
+        <v>15.70874691009521</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>70.47618865966797</v>
+        <v>27.18253898620605</v>
       </c>
       <c r="B52" t="n">
-        <v>65.54734039306641</v>
+        <v>28.11896324157715</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>12.5</v>
+        <v>24.79999923706055</v>
       </c>
       <c r="B53" t="n">
-        <v>10.73054218292236</v>
+        <v>55.94216918945312</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>27.71792411804199</v>
+        <v>22.5</v>
       </c>
       <c r="B54" t="n">
-        <v>25.84085845947266</v>
+        <v>15.46550941467285</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>27.22820854187012</v>
+        <v>36.63075256347656</v>
       </c>
       <c r="B55" t="n">
-        <v>24.58513641357422</v>
+        <v>16.42928504943848</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6.0724778175354</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="B56" t="n">
-        <v>11.48751163482666</v>
+        <v>11.06066513061523</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>12.69841289520264</v>
+        <v>46.70000076293945</v>
       </c>
       <c r="B57" t="n">
-        <v>15.49434089660645</v>
+        <v>18.05863571166992</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>17.36111068725586</v>
+        <v>14.6245059967041</v>
       </c>
       <c r="B58" t="n">
-        <v>20.51945877075195</v>
+        <v>17.58055877685547</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>24.10000038146973</v>
+        <v>34.70000076293945</v>
       </c>
       <c r="B59" t="n">
-        <v>23.17951965332031</v>
+        <v>20.18341064453125</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>12.54940700531006</v>
+        <v>45.52381134033203</v>
       </c>
       <c r="B60" t="n">
-        <v>12.68120670318604</v>
+        <v>40.57023239135742</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>20.83333396911621</v>
+        <v>25.95494651794434</v>
       </c>
       <c r="B61" t="n">
-        <v>23.1657657623291</v>
+        <v>28.44570922851562</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>32.41919708251953</v>
+        <v>12.99603176116943</v>
       </c>
       <c r="B62" t="n">
-        <v>32.03214645385742</v>
+        <v>35.56428909301758</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>19.09892272949219</v>
+        <v>13.2380952835083</v>
       </c>
       <c r="B63" t="n">
-        <v>18.20249938964844</v>
+        <v>16.63674736022949</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>36.63075256347656</v>
+        <v>68.85713958740234</v>
       </c>
       <c r="B64" t="n">
-        <v>23.83972549438477</v>
+        <v>62.55885696411133</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>10.91269874572754</v>
+        <v>8.227228164672852</v>
       </c>
       <c r="B65" t="n">
-        <v>18.91648864746094</v>
+        <v>14.18759441375732</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>32.41919708251953</v>
+        <v>54.66666793823242</v>
       </c>
       <c r="B66" t="n">
-        <v>32.03214645385742</v>
+        <v>64.54462432861328</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>8.227228164672852</v>
+        <v>11.4285717010498</v>
       </c>
       <c r="B67" t="n">
-        <v>9.61054801940918</v>
+        <v>12.75198459625244</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>26.98412704467773</v>
+        <v>14.1304349899292</v>
       </c>
       <c r="B68" t="n">
-        <v>28.10575485229492</v>
+        <v>15.39330005645752</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>44.57143020629883</v>
+        <v>9.809523582458496</v>
       </c>
       <c r="B69" t="n">
-        <v>57.23471069335938</v>
+        <v>14.1047191619873</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>19.84127044677734</v>
+        <v>25.09920692443848</v>
       </c>
       <c r="B70" t="n">
-        <v>31.5500602722168</v>
+        <v>26.83688163757324</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>40.27777862548828</v>
+        <v>14</v>
       </c>
       <c r="B71" t="n">
-        <v>19.45535659790039</v>
+        <v>15.73022270202637</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>30.19047546386719</v>
+        <v>28.5</v>
       </c>
       <c r="B72" t="n">
-        <v>26.36160087585449</v>
+        <v>24.84612846374512</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>33.39862823486328</v>
+        <v>15.083251953125</v>
       </c>
       <c r="B73" t="n">
-        <v>27.49152755737305</v>
+        <v>16.41362953186035</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>53.20000076293945</v>
+        <v>29.39999961853027</v>
       </c>
       <c r="B74" t="n">
-        <v>38.40982818603516</v>
+        <v>28.7347412109375</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>43.79999923706055</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="B75" t="n">
-        <v>45.8603630065918</v>
+        <v>14.94832038879395</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>15.083251953125</v>
+        <v>24.87757110595703</v>
       </c>
       <c r="B76" t="n">
-        <v>11.91039085388184</v>
+        <v>27.40260887145996</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>19.58863830566406</v>
+        <v>92.90000152587891</v>
       </c>
       <c r="B77" t="n">
-        <v>28.26310729980469</v>
+        <v>88.28484344482422</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>10.7737512588501</v>
+        <v>23</v>
       </c>
       <c r="B78" t="n">
-        <v>9.88310432434082</v>
+        <v>31.03679084777832</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>20.33730125427246</v>
+        <v>25.6611156463623</v>
       </c>
       <c r="B79" t="n">
-        <v>20.00243186950684</v>
+        <v>29.29222297668457</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>40</v>
+        <v>22.6248779296875</v>
       </c>
       <c r="B80" t="n">
-        <v>53.8125</v>
+        <v>12.82931423187256</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>100</v>
+        <v>20.47012710571289</v>
       </c>
       <c r="B81" t="n">
-        <v>92.44561767578125</v>
+        <v>20.92783546447754</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6.660137176513672</v>
+        <v>38.39373016357422</v>
       </c>
       <c r="B82" t="n">
-        <v>10.79543781280518</v>
+        <v>28.45419692993164</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>26.05288887023926</v>
+        <v>27.71792411804199</v>
       </c>
       <c r="B83" t="n">
-        <v>24.22736167907715</v>
+        <v>25.99479866027832</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>42.19047546386719</v>
+        <v>34.09999847412109</v>
       </c>
       <c r="B84" t="n">
-        <v>22.67095184326172</v>
+        <v>31.38720512390137</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>35.5</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="B85" t="n">
-        <v>28.00699043273926</v>
+        <v>31.28963088989258</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>45.80952453613281</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="B86" t="n">
-        <v>47.16511917114258</v>
+        <v>17.38893890380859</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>17.94871711730957</v>
+        <v>74.28571319580078</v>
       </c>
       <c r="B87" t="n">
-        <v>18.66628074645996</v>
+        <v>69.60839080810547</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>100</v>
+        <v>25.39682579040527</v>
       </c>
       <c r="B88" t="n">
-        <v>94.64259338378906</v>
+        <v>28.13515663146973</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>12.99603176116943</v>
+        <v>3.917727708816528</v>
       </c>
       <c r="B89" t="n">
-        <v>44.15458297729492</v>
+        <v>19.54708099365234</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>68.5</v>
+        <v>11</v>
       </c>
       <c r="B90" t="n">
-        <v>64.83039093017578</v>
+        <v>13.2954683303833</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>46.70000076293945</v>
+        <v>27.79999923706055</v>
       </c>
       <c r="B91" t="n">
-        <v>33.39981842041016</v>
+        <v>9.148971557617188</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>20</v>
+        <v>14.20176315307617</v>
       </c>
       <c r="B92" t="n">
-        <v>23.82773017883301</v>
+        <v>14.38733673095703</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>36.5</v>
+        <v>87.80000305175781</v>
       </c>
       <c r="B93" t="n">
-        <v>29.02987098693848</v>
+        <v>88.11577606201172</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>26.09127044677734</v>
+        <v>5.221674919128418</v>
       </c>
       <c r="B94" t="n">
-        <v>20.57485389709473</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>28.7952995300293</v>
-      </c>
-      <c r="B95" t="n">
-        <v>34.5872688293457</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>10.34482765197754</v>
-      </c>
-      <c r="B96" t="n">
-        <v>10.66494464874268</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>99.20635223388672</v>
-      </c>
-      <c r="B97" t="n">
-        <v>90.79053497314453</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>39.09999847412109</v>
-      </c>
-      <c r="B98" t="n">
-        <v>52.19807434082031</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>16.5714282989502</v>
-      </c>
-      <c r="B99" t="n">
-        <v>18.48725128173828</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>23.11459350585938</v>
-      </c>
-      <c r="B100" t="n">
-        <v>23.70133972167969</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>11.65524005889893</v>
-      </c>
-      <c r="B101" t="n">
-        <v>13.04542827606201</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>27.79999923706055</v>
-      </c>
-      <c r="B102" t="n">
-        <v>26.9631404876709</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>23</v>
-      </c>
-      <c r="B103" t="n">
-        <v>21.62454795837402</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>44.70000076293945</v>
-      </c>
-      <c r="B104" t="n">
-        <v>45.4066162109375</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>5.320197105407715</v>
-      </c>
-      <c r="B105" t="n">
-        <v>11.09067440032959</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>39.68254089355469</v>
-      </c>
-      <c r="B106" t="n">
-        <v>55.01422500610352</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>10.34482765197754</v>
-      </c>
-      <c r="B107" t="n">
-        <v>10.66494464874268</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="B108" t="n">
-        <v>86.94750213623047</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>31</v>
-      </c>
-      <c r="B109" t="n">
-        <v>29.00503540039062</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>6.502462863922119</v>
-      </c>
-      <c r="B110" t="n">
-        <v>6.882169246673584</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>23.5238094329834</v>
-      </c>
-      <c r="B111" t="n">
-        <v>27.44560241699219</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>22.9187068939209</v>
-      </c>
-      <c r="B112" t="n">
-        <v>24.17636871337891</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>17.53183174133301</v>
-      </c>
-      <c r="B113" t="n">
-        <v>15.31678867340088</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>27.18253898620605</v>
-      </c>
-      <c r="B114" t="n">
-        <v>24.26395416259766</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>40.20000076293945</v>
-      </c>
-      <c r="B115" t="n">
-        <v>34.00544738769531</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>46.20000076293945</v>
-      </c>
-      <c r="B116" t="n">
-        <v>34.13157272338867</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>34.70000076293945</v>
-      </c>
-      <c r="B117" t="n">
-        <v>27.43224334716797</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>97.94319152832031</v>
-      </c>
-      <c r="B118" t="n">
-        <v>85.42715454101562</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>95.23809814453125</v>
-      </c>
-      <c r="B119" t="n">
-        <v>87.47099304199219</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>80.69999694824219</v>
-      </c>
-      <c r="B120" t="n">
-        <v>76.72212219238281</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>31.84523773193359</v>
-      </c>
-      <c r="B121" t="n">
-        <v>30.38090896606445</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>20</v>
-      </c>
-      <c r="B122" t="n">
-        <v>47.7126350402832</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>54.66666793823242</v>
-      </c>
-      <c r="B123" t="n">
-        <v>53.5909309387207</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>59.52381134033203</v>
-      </c>
-      <c r="B124" t="n">
-        <v>63.58428573608398</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>34.09999847412109</v>
-      </c>
-      <c r="B125" t="n">
-        <v>30.9416561126709</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>19.74206352233887</v>
-      </c>
-      <c r="B126" t="n">
-        <v>15.97398948669434</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="B127" t="n">
-        <v>22.54209518432617</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>39.17727661132812</v>
-      </c>
-      <c r="B128" t="n">
-        <v>41.39523696899414</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>39.68254089355469</v>
-      </c>
-      <c r="B129" t="n">
-        <v>43.53192520141602</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>58.76591491699219</v>
-      </c>
-      <c r="B130" t="n">
-        <v>65.87525939941406</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>24.87757110595703</v>
-      </c>
-      <c r="B131" t="n">
-        <v>23.01767539978027</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>27.23809432983398</v>
-      </c>
-      <c r="B132" t="n">
-        <v>17.54653358459473</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>19.0476188659668</v>
-      </c>
-      <c r="B133" t="n">
-        <v>25.53112983703613</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>17.53183174133301</v>
-      </c>
-      <c r="B134" t="n">
-        <v>15.31678867340088</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>25.6611156463623</v>
-      </c>
-      <c r="B135" t="n">
-        <v>23.53068923950195</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>60</v>
-      </c>
-      <c r="B136" t="n">
-        <v>57.78901290893555</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>20.47012710571289</v>
-      </c>
-      <c r="B137" t="n">
-        <v>23.83867835998535</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>20</v>
-      </c>
-      <c r="B138" t="n">
-        <v>30.42439079284668</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>59.52381134033203</v>
-      </c>
-      <c r="B139" t="n">
-        <v>58.87971878051758</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>34.09999847412109</v>
-      </c>
-      <c r="B140" t="n">
-        <v>30.9416561126709</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>40.20000076293945</v>
-      </c>
-      <c r="B141" t="n">
-        <v>34.00544738769531</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>74.28571319580078</v>
-      </c>
-      <c r="B142" t="n">
-        <v>71.14609527587891</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>25.39682579040527</v>
-      </c>
-      <c r="B143" t="n">
-        <v>18.80481719970703</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>3.917727708816528</v>
-      </c>
-      <c r="B144" t="n">
-        <v>10.36193656921387</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>21.5475025177002</v>
-      </c>
-      <c r="B145" t="n">
-        <v>24.30719184875488</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>87.80000305175781</v>
-      </c>
-      <c r="B146" t="n">
-        <v>82.77976226806641</v>
+        <v>7.232016086578369</v>
       </c>
     </row>
   </sheetData>
